--- a/tools/docgen/out/3대-수출시장-비교표.xlsx
+++ b/tools/docgen/out/3대-수출시장-비교표.xlsx
@@ -748,7 +748,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6031995E-AA1C-488F-9981-ED3187AEF91B}</x14:id>
+          <x14:id>{732BE06D-B661-4F99-9970-3FBCAA2DAE53}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -762,7 +762,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C1740DB0-0B7B-48E7-B05C-AAB75B384AA7}</x14:id>
+          <x14:id>{8EC69362-2053-4394-9A54-DD451013A022}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -773,7 +773,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6031995E-AA1C-488F-9981-ED3187AEF91B}">
+          <x14:cfRule type="dataBar" id="{732BE06D-B661-4F99-9970-3FBCAA2DAE53}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -786,7 +786,7 @@
           <xm:sqref>C6:C8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C1740DB0-0B7B-48E7-B05C-AAB75B384AA7}">
+          <x14:cfRule type="dataBar" id="{8EC69362-2053-4394-9A54-DD451013A022}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
